--- a/public/assets/file/format_ruangan_last.xlsx
+++ b/public/assets/file/format_ruangan_last.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="8">
   <si>
     <t>nama ruangan</t>
   </si>
@@ -36,6 +36,9 @@
   </si>
   <si>
     <t>2024-2025 Ganjil</t>
+  </si>
+  <si>
+    <t>2024-2025 Genap</t>
   </si>
 </sst>
 </file>
@@ -429,7 +432,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="18.54296875" customWidth="true" style="0"/>
@@ -482,6 +485,14 @@
         <v>6</v>
       </c>
     </row>
+    <row r="6" spans="1:5">
+      <c r="D6">
+        <v>4</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="D1:E1"/>
